--- a/integration-tests/src/test/resources/enchilada.xlsx
+++ b/integration-tests/src/test/resources/enchilada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\my_projects\springeq\web-application-quickstart-springboot\integration-tests\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9736731D-E52D-4CCF-88E3-77A154E45144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5C008A-8A07-48BE-9378-9A21C66DC2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13770" yWindow="4605" windowWidth="35325" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,10 +62,10 @@
     <t>Yatta yatta 2</t>
   </si>
   <si>
-    <t>{ id: 1}</t>
-  </si>
-  <si>
-    <t>{ id: 2}</t>
+    <t>{ "id": 1}</t>
+  </si>
+  <si>
+    <t>{ "id": 2}</t>
   </si>
 </sst>
 </file>
